--- a/ci-cd-merge-resolver/repoCollector/datasets/azure-sdk-for-java.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/azure-sdk-for-java.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="407">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,6 +44,24 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>cac3f5e90227a9dbb2395ee99d4bdcf95f63ce06</t>
+  </si>
+  <si>
+    <t>d839f607f69c3b00674060b3fdd97cbe3d78f2f0</t>
+  </si>
+  <si>
+    <t>3e7a4b2eeccf08c65a605a7604ead9bb5f3ba934</t>
+  </si>
+  <si>
+    <t>fb2502eb45e95e7e6cb7a71d4f7a968bafe2b156</t>
+  </si>
+  <si>
+    <t>b852fcd100e0e609c105d9c17e6810b36d2d8108</t>
+  </si>
+  <si>
+    <t>eec634475556369c7fb2a3b8b564941846637412</t>
+  </si>
+  <si>
     <t>14580eac407a3c1d14d6f07bbd9c67e8262cfea7</t>
   </si>
   <si>
@@ -53,6 +71,195 @@
     <t>04fca4a89d67312b4d5ce361c058c675274a7880</t>
   </si>
   <si>
+    <t>71ec0e2368673e26e501aa2a1ced8bb06b3d6122</t>
+  </si>
+  <si>
+    <t>e2f99afe39451bd4766f482bfaa1687c6e3321d7</t>
+  </si>
+  <si>
+    <t>d5fbbfdb38fb17944a0df5124a1893fe08d4533f</t>
+  </si>
+  <si>
+    <t>f19226e54cd725217a919a3be51f8f8ee797787d</t>
+  </si>
+  <si>
+    <t>9043b2c7b7ee88b531dfe34ed413f7deb656052f</t>
+  </si>
+  <si>
+    <t>fb890ccd34c9652ff3e9656b6fca012f4693de1a</t>
+  </si>
+  <si>
+    <t>e63b88bbfe0ab0dc344a52a8c1bfc2d7ad61697c</t>
+  </si>
+  <si>
+    <t>8a773eb21476eae63faf29e329bbdf200b9c07dc</t>
+  </si>
+  <si>
+    <t>e47df8f3ccb771dd897e16d38fa143453f50bfc9</t>
+  </si>
+  <si>
+    <t>53bbca676710f43ca48b466de9f068a2d522efae</t>
+  </si>
+  <si>
+    <t>db8e593b1eb66938cc32a6c339eef962f99f3639</t>
+  </si>
+  <si>
+    <t>a58b7de53784527a2b0c88ecf109e0b393ce47cb</t>
+  </si>
+  <si>
+    <t>4c6fc39f7ec297f5c980d1d739292380d3a6f551</t>
+  </si>
+  <si>
+    <t>f9f781c562e4330136259afcc16611b68e94ca2d</t>
+  </si>
+  <si>
+    <t>d78f9c30de914dffd4c394a6d7d30628c82fabe3</t>
+  </si>
+  <si>
+    <t>8a123464d62cbd5ba0b4b2049d201465e94af410</t>
+  </si>
+  <si>
+    <t>14705e4cd6237630023f0cb9f5d5e92b01e4cccd</t>
+  </si>
+  <si>
+    <t>dcacb470e1c3991b4a831c86218e2d83edbf82bd</t>
+  </si>
+  <si>
+    <t>80e6cfca73a3cd3c83a86ffe80280e96359cda8c</t>
+  </si>
+  <si>
+    <t>8a45ba30c909c61757d0acd860d5923b7a567bf5</t>
+  </si>
+  <si>
+    <t>c67affbef4dd218318b0dfa2e49d21d3921434c3</t>
+  </si>
+  <si>
+    <t>9abc43d99912c9a4ce43a21d09b585d11fd0dd9f</t>
+  </si>
+  <si>
+    <t>5ae811d87d882a23b7a890ee68f4f1d11b1617fc</t>
+  </si>
+  <si>
+    <t>6d760562814ecca49a2dbc2076169ca98cd587da</t>
+  </si>
+  <si>
+    <t>756a2791257b81043fd8db9b08bdbdd713762467</t>
+  </si>
+  <si>
+    <t>df0ca11a68553e3bc129c89bc432b13e02bf6d38</t>
+  </si>
+  <si>
+    <t>f49e8b1d9a17378a8798dbecc7fc5c1bb5f41040</t>
+  </si>
+  <si>
+    <t>d58b9171db3743f6705663769d2cd1e9c00c4a8b</t>
+  </si>
+  <si>
+    <t>e22d112611404bb2371bcd3472919d48672573fb</t>
+  </si>
+  <si>
+    <t>eb62537403a45d50d0a03476a5d679388d3b347d</t>
+  </si>
+  <si>
+    <t>9e11b42ea34060054238943e684f79db8bab890f</t>
+  </si>
+  <si>
+    <t>b8ac2c2d18d1811b30bdc66e4a6aa349797b1b62</t>
+  </si>
+  <si>
+    <t>3583b872adbeb8568389f9ec659a5c81ef2fa53d</t>
+  </si>
+  <si>
+    <t>611ddc1e25fa89ed922d7def5daeb6ae9faa3cd6</t>
+  </si>
+  <si>
+    <t>521ffa506fc4a19892343f26009238a23c24d124</t>
+  </si>
+  <si>
+    <t>5c0c257afdf5e30f12e31729a2ecac3721a0169f</t>
+  </si>
+  <si>
+    <t>b7cec419659f54d764892344b6bf8974917375ad</t>
+  </si>
+  <si>
+    <t>77b328a12cbe0bd79477351b93a42c987a469d04</t>
+  </si>
+  <si>
+    <t>14d5a09b8184e5dc0030f8bc4ba68e5f60abc109</t>
+  </si>
+  <si>
+    <t>34c778d6c9d47cf7b7554a4bf622ea3d149e31c6</t>
+  </si>
+  <si>
+    <t>05d7a41db90603e74a05df1da8776c0aab7c1258</t>
+  </si>
+  <si>
+    <t>e51e405e27d7d72ff5152553252587c1e2293e3c</t>
+  </si>
+  <si>
+    <t>d53caccd21ffd1e1e5a068f7af85047e06a502b2</t>
+  </si>
+  <si>
+    <t>5a3e89b8e6d4c95b036fb8502d1629286580c97f</t>
+  </si>
+  <si>
+    <t>c4b1f7700f489efc64c7413eeadb62cb7a82045a</t>
+  </si>
+  <si>
+    <t>33f4a92492d2a996ca04004bac8ef3753c59c4ae</t>
+  </si>
+  <si>
+    <t>ca9b2e71fe6f369fb95c97a67175172d0d8cc8b9</t>
+  </si>
+  <si>
+    <t>cec906c220582a59dc07d7a8b9751c73ccdb3bf5</t>
+  </si>
+  <si>
+    <t>cc553dfdf9f47b7f5a31b625d60e705d593ae6d7</t>
+  </si>
+  <si>
+    <t>c6e2ce7062424cfadc906926a00ab73353f7cd4d</t>
+  </si>
+  <si>
+    <t>ee66c8a7baf78d01d1d08ce29c8cf94f239d656f</t>
+  </si>
+  <si>
+    <t>69f21008e6ed9c3bb7aca835e5e0a89379a90209</t>
+  </si>
+  <si>
+    <t>0db5366fa3b37690179c5d26daae08b51cbb0da2</t>
+  </si>
+  <si>
+    <t>18c372fbe99167f19ccb4f41e036a96095450d4b</t>
+  </si>
+  <si>
+    <t>2af39e3311bcd863f656a6062f7e84c7ad293e39</t>
+  </si>
+  <si>
+    <t>5cbef3b9fa9395c413e169e7c16a2cfddf94d5cd</t>
+  </si>
+  <si>
+    <t>fb1fbcbd14188ea3c4613c27e4223f07d3f450b3</t>
+  </si>
+  <si>
+    <t>c5fd699e9a88765ff91f9df8523477927e123698</t>
+  </si>
+  <si>
+    <t>d1f993a354aa0e19cef4274913136b61381a6884</t>
+  </si>
+  <si>
+    <t>b24e6fdce8d74f076ff8a0379115a1b33697efdb</t>
+  </si>
+  <si>
+    <t>e513828cf75d7202124cdd47570b2c93e73a92e2</t>
+  </si>
+  <si>
+    <t>29f50d61ebcd59df962d1cce7a9c896cf5c6af94</t>
+  </si>
+  <si>
+    <t>5755604f39c7eea6f99994c49164ae4c60c2db8c</t>
+  </si>
+  <si>
     <t>07a458ce20e376e7a753685c4f1f19b93dd9ac8e</t>
   </si>
   <si>
@@ -62,6 +269,33 @@
     <t>77be025a284db25a14536a98d31234642ccd3eaa</t>
   </si>
   <si>
+    <t>584a9fd2a4bc308ddbb34295e5ed71bacf68d0f0</t>
+  </si>
+  <si>
+    <t>4b873f3d873faf0ed6526b6a0b868384832424a6</t>
+  </si>
+  <si>
+    <t>f67148fda361c0608a9af82a0ce0db60c2544282</t>
+  </si>
+  <si>
+    <t>f94efd480fd647b247257ae81f5d20ba24a6efb2</t>
+  </si>
+  <si>
+    <t>1de42f8059b26a78f02ecc8f04b00a8d547b2aa7</t>
+  </si>
+  <si>
+    <t>08e7fdaa0703991f2547a85f618b86eb47b7bc59</t>
+  </si>
+  <si>
+    <t>72394e55ef9e01dad56d2966787d826fe5613f89</t>
+  </si>
+  <si>
+    <t>0ef36eb82d67a9027866698d56fdc7767bd33cbe</t>
+  </si>
+  <si>
+    <t>21a0f7a386cbd963566b0ad2ce1059eb1cff0dd9</t>
+  </si>
+  <si>
     <t>1a8d7cda3df5e5b880072d2776aa416fad95d6fc</t>
   </si>
   <si>
@@ -71,31 +305,355 @@
     <t>81efb73334e316261151bb0751e59210dd4d1df0</t>
   </si>
   <si>
-    <t>72394e55ef9e01dad56d2966787d826fe5613f89</t>
-  </si>
-  <si>
-    <t>0ef36eb82d67a9027866698d56fdc7767bd33cbe</t>
-  </si>
-  <si>
-    <t>21a0f7a386cbd963566b0ad2ce1059eb1cff0dd9</t>
-  </si>
-  <si>
-    <t>2af39e3311bcd863f656a6062f7e84c7ad293e39</t>
-  </si>
-  <si>
-    <t>5cbef3b9fa9395c413e169e7c16a2cfddf94d5cd</t>
-  </si>
-  <si>
-    <t>fb1fbcbd14188ea3c4613c27e4223f07d3f450b3</t>
-  </si>
-  <si>
-    <t>c6e2ce7062424cfadc906926a00ab73353f7cd4d</t>
-  </si>
-  <si>
-    <t>ee66c8a7baf78d01d1d08ce29c8cf94f239d656f</t>
-  </si>
-  <si>
-    <t>69f21008e6ed9c3bb7aca835e5e0a89379a90209</t>
+    <t>cd0d59a87e1547108050aa930206948a765f5786</t>
+  </si>
+  <si>
+    <t>9578b3d5d237524d2d09f5fe631f689647ca2759</t>
+  </si>
+  <si>
+    <t>f83d9f1cb256af83bcc3ec99b4b2d8964b88081e</t>
+  </si>
+  <si>
+    <t>33e4b32f5e4d58ae8314623fcf35c976179ca323</t>
+  </si>
+  <si>
+    <t>adfc66c55993fbbc64979f208ea8e46d66c4c6b5</t>
+  </si>
+  <si>
+    <t>f9b92161e55a670332dc9886da5f70df5b8d5f8f</t>
+  </si>
+  <si>
+    <t>9d10b896f4e153067688308f5fe2ae67061f5a49</t>
+  </si>
+  <si>
+    <t>ddd0550bb406839509c0d4bc6f76bcfd7015a0ad</t>
+  </si>
+  <si>
+    <t>952c1da90c98116d62b902b87f13ece224d728cf</t>
+  </si>
+  <si>
+    <t>7a67f216edbedd9b9142106ab4ac6aa2e737f6a4</t>
+  </si>
+  <si>
+    <t>8aa924d7fc0d523b9143d9e1d2ef733b338334db</t>
+  </si>
+  <si>
+    <t>1a8a814a4b8525983c42d8fdc554da6f69d10fed</t>
+  </si>
+  <si>
+    <t>c7060d227669b7a78e020f1e1659c3ba964b9563</t>
+  </si>
+  <si>
+    <t>4c6802336d9cc270115700fd0a9cdf2446721995</t>
+  </si>
+  <si>
+    <t>1d33612311d212dd8117163e0725e02df13c9fff</t>
+  </si>
+  <si>
+    <t>85ab97fce59e580bbe64b81ef8c7d09d6e7325ac</t>
+  </si>
+  <si>
+    <t>fd832fc5d3948968ecc2a5fc7752cdc71914c82f</t>
+  </si>
+  <si>
+    <t>47b03dfd13f65260833c474f2fe62efa8eb91b73</t>
+  </si>
+  <si>
+    <t>5063be74bb9055a9b84a84544032b97a554ff7e5</t>
+  </si>
+  <si>
+    <t>28ffe01e71db927f661ad41c8ac037911f64781c</t>
+  </si>
+  <si>
+    <t>f81336379ff0a91f402be049fa5e983f78e26b9c</t>
+  </si>
+  <si>
+    <t>91413926321538c4e03a25556b1c3f72e6c49b22</t>
+  </si>
+  <si>
+    <t>efb23cef279f9cc635ea12ebfc6002f7c77c14f0</t>
+  </si>
+  <si>
+    <t>5c64f79e9b77460f53bcf7fa4e8369981430083a</t>
+  </si>
+  <si>
+    <t>2c1dd9f09c71d381bd14c1b4eb7e49a435896890</t>
+  </si>
+  <si>
+    <t>118f3f2fc7298c15e1394b3348839ae570e2e833</t>
+  </si>
+  <si>
+    <t>c346b8acb0a8512a01650275ccc18fb4aea5424d</t>
+  </si>
+  <si>
+    <t>2a6c3fa9f8e1699364d75eee242fbc660ba0a98b</t>
+  </si>
+  <si>
+    <t>2316c8033bffb6b70e3f812966bee633e9e95eb6</t>
+  </si>
+  <si>
+    <t>cb70aceceaec041159b006b85c8805c24dd72e07</t>
+  </si>
+  <si>
+    <t>827ff03d385c2dcfec0cab9ef29536d51e5832b1</t>
+  </si>
+  <si>
+    <t>3e1278ee732f3e8814c8fbaee3ee718732664842</t>
+  </si>
+  <si>
+    <t>1444c6d105c9c993911c4fcec23a36a825018dd5</t>
+  </si>
+  <si>
+    <t>e7f532bc0b790e8f180f0b0687125455f78cec01</t>
+  </si>
+  <si>
+    <t>00b65c0cf52b97e37786732db6671e240394e95e</t>
+  </si>
+  <si>
+    <t>6a25c24bd964a018734860b110bc1d3be306088e</t>
+  </si>
+  <si>
+    <t>d83623634fb2632f8310a9571aa26dba003a1f09</t>
+  </si>
+  <si>
+    <t>42468d0da2861216b6bee79de1632f2f5a181ee6</t>
+  </si>
+  <si>
+    <t>f37f0482dc4a994ece44498d84d5a4d6802b9b89</t>
+  </si>
+  <si>
+    <t>699e2ee0a75b1a3dc76f088332b65150b171d995</t>
+  </si>
+  <si>
+    <t>b5fbe5bd7742f2b605fd6d172329885e3483251f</t>
+  </si>
+  <si>
+    <t>f206c4821a4532a86de8706c9a347edaccca5bbd</t>
+  </si>
+  <si>
+    <t>f4b258024a6b6b62d8c703ab71bbc8996a053656</t>
+  </si>
+  <si>
+    <t>4002c95cda9521f2349ce22ca96ce1cc8ffc5ae6</t>
+  </si>
+  <si>
+    <t>8e17a3ad07181d047768932fbaac9d9d46538565</t>
+  </si>
+  <si>
+    <t>d000bd591c9816079281cc4ef2cceca47a33dd34</t>
+  </si>
+  <si>
+    <t>26754bcfd8af4ee89cb8869940a38074567e7046</t>
+  </si>
+  <si>
+    <t>6756f8635e42e92166a0ab5787530e421fdd2082</t>
+  </si>
+  <si>
+    <t>0419b3c801ac18ae0aad814a15ba4a1ccc8c51ce</t>
+  </si>
+  <si>
+    <t>d73b34c958c5c0fd769f6942993ddfeeed688e07</t>
+  </si>
+  <si>
+    <t>ece6b1553732395a695db0333b19b6f590b45244</t>
+  </si>
+  <si>
+    <t>2fe1109ce793a088845c2a520d88871514563536</t>
+  </si>
+  <si>
+    <t>f055f3d243d2bbbb2b50ad7a8392748c44ac22de</t>
+  </si>
+  <si>
+    <t>50cd97c15614a615e4403381fafde240fe578be9</t>
+  </si>
+  <si>
+    <t>ba60d2ba39f1e5b186679757f999b1f14648b55b</t>
+  </si>
+  <si>
+    <t>faca7a59448788b7a6a5dcde8ac54ad758beedf8</t>
+  </si>
+  <si>
+    <t>c8c3d31000dd549f1cb8f4a0df0a36716b94b651</t>
+  </si>
+  <si>
+    <t>7d54b0e39d286b5c0138b22ffb6d89c66aa7895c</t>
+  </si>
+  <si>
+    <t>932f059bbef407a3aa5f76124bdcaef2b55c648f</t>
+  </si>
+  <si>
+    <t>60b57af57435c1910947732eae580951c775aa1e</t>
+  </si>
+  <si>
+    <t>9c1c971475923970244153a9ed0b44993b969786</t>
+  </si>
+  <si>
+    <t>89f5be14ed36f45346dc69009f7d6e095cf5f890</t>
+  </si>
+  <si>
+    <t>faf7e608608de9a5cc1bc9816cb19cff577dfbdf</t>
+  </si>
+  <si>
+    <t>bd6f90256f8b0a1c60b8f4abba28126a1e140095</t>
+  </si>
+  <si>
+    <t>85b47e7836dd36c48cd60a113d8806f0129cee72</t>
+  </si>
+  <si>
+    <t>60982d67acf61984ac3340a2e0b3f441d6e85694</t>
+  </si>
+  <si>
+    <t>aae876e168f26d08ee9efac9e24d873b7e24a735</t>
+  </si>
+  <si>
+    <t>5a1fe8abc7e44a7477321ba20c2f321167b4a214</t>
+  </si>
+  <si>
+    <t>553fa4c5a19cf759009743e25b2cd70a475e9703</t>
+  </si>
+  <si>
+    <t>163b3899088d6086edd5e51c97155872176aaefb</t>
+  </si>
+  <si>
+    <t>64c3003dddbeb4496621e6200da90a09cd296fd7</t>
+  </si>
+  <si>
+    <t>f202ab8dc4dcb11dc8128ecd00f2aed1fef86fe6</t>
+  </si>
+  <si>
+    <t>723b4fe574a3b89bac9b0d8819fe9faa3d7c729d</t>
+  </si>
+  <si>
+    <t>7d5f4ac65d194293c0d95fa73f3ebbca7eb1dc31</t>
+  </si>
+  <si>
+    <t>92ca539f73869b92c932fbae141c986ea98c9742</t>
+  </si>
+  <si>
+    <t>c79315340bf7bc1b912b627ce642419333d9de49</t>
+  </si>
+  <si>
+    <t>b14fc66828adf99887d8cdc3cd9efb020301cc27</t>
+  </si>
+  <si>
+    <t>209d10cef00ada55442d6c38d0bcf6d8c17751fa</t>
+  </si>
+  <si>
+    <t>b4222faf481a981d05411c3bc2ceeceaa6f26611</t>
+  </si>
+  <si>
+    <t>3103a270b96deaf9f5a1d8fb5ea76c2464c66582</t>
+  </si>
+  <si>
+    <t>93719f3cdfe462d94161d1364c8ec03c55794f81</t>
+  </si>
+  <si>
+    <t>4d2ebfb99b900709e2ebc504545e21b7eb8e01db</t>
+  </si>
+  <si>
+    <t>7f4a70dbf54cf83bf6dfdb76009ecc6578a0e7c5</t>
+  </si>
+  <si>
+    <t>a5347a1ed2a1c15356d9718c926a1175c3434881</t>
+  </si>
+  <si>
+    <t>2351d8e74ca5770f8264515d8575838be61c5649</t>
+  </si>
+  <si>
+    <t>d9ab47ab17174aa188c5f661f7ebba55c7c45006</t>
+  </si>
+  <si>
+    <t>cb5d69f26c4b3becc4f04f36ea924eda4731b4fb</t>
+  </si>
+  <si>
+    <t>7ff0d2f1fc9a0370bc40be2e7d17e2bdc25432b4</t>
+  </si>
+  <si>
+    <t>2100d2af3198ab98e06aa38114fe801de78b324b</t>
+  </si>
+  <si>
+    <t>1de40d81f890e6aeb9218689b57dfe2152227c16</t>
+  </si>
+  <si>
+    <t>9ef845e20b608e67483e69ead1c67405a22fcdb5</t>
+  </si>
+  <si>
+    <t>29a87d1562258f07f91f424bba7afb70b482701a</t>
+  </si>
+  <si>
+    <t>d4748b852a5da3a365ba1962c04de3ad0c2e6d8e</t>
+  </si>
+  <si>
+    <t>122f5820ed650db7efb23681f3ae5299a5a4498e</t>
+  </si>
+  <si>
+    <t>104a632c35e2120382fa76c551a7f226774e0c78</t>
+  </si>
+  <si>
+    <t>1969d61d8561d788cb2ea504ca88158ee7aa898c</t>
+  </si>
+  <si>
+    <t>8e7e9c060aa52bc25ed4af1062952440c2c279cd</t>
+  </si>
+  <si>
+    <t>f929439c742061dd3f33c6f14b9522c3045ac609</t>
+  </si>
+  <si>
+    <t>7a0b0c3123484700f6f43c0ad520ca23e93c8f8c</t>
+  </si>
+  <si>
+    <t>0c73841e7b29527354d4d6e8bf1449ddb6df7905</t>
+  </si>
+  <si>
+    <t>1d9a3df69051250f68fa4a9aecd7322cf06ceb8c</t>
+  </si>
+  <si>
+    <t>7997eaa0acff7c15a6954016e4ea7ffbe248bf33</t>
+  </si>
+  <si>
+    <t>014f18bda15328898ce6f1d21bab90121ec9a392</t>
+  </si>
+  <si>
+    <t>3ad36bafe57bf574a1b10e809e12a76cc3865f8e</t>
+  </si>
+  <si>
+    <t>157e4b82aaff377d6e0900cbc9689e695a4f3e11</t>
+  </si>
+  <si>
+    <t>70994a66e56b174d596ab91508b5d380ec6987c2</t>
+  </si>
+  <si>
+    <t>89807ae53b36bf98c7d0d9a4802ad6f4fd03c027</t>
+  </si>
+  <si>
+    <t>c7756b18607c61a9455f344917773194301083ef</t>
+  </si>
+  <si>
+    <t>205a6d481baf43cfda80c3fab770538fb42bf281</t>
+  </si>
+  <si>
+    <t>b46ec7e7c22dd17e8d495ce63c13ad14f6b41132</t>
+  </si>
+  <si>
+    <t>65d59d6f659b227b9936911c99f9cd053249af86</t>
+  </si>
+  <si>
+    <t>832214f63931908c416a745e2e30b6cf683b6812</t>
+  </si>
+  <si>
+    <t>54bbd743201901b79be013868d7a2f9a9766b331</t>
+  </si>
+  <si>
+    <t>dc9cf4f0b75ac3672a3e125fa2b905dcab7d46f1</t>
+  </si>
+  <si>
+    <t>6d6a24e47a4254f6c97665d5e5d2b7b3f436674b</t>
+  </si>
+  <si>
+    <t>a4383fd7412f0159f98aa14c6f20a5609c79294e</t>
+  </si>
+  <si>
+    <t>63e922f92aee8a3bcbfbc2218a590398337b11fd</t>
   </si>
   <si>
     <t>5457eb044ebdcf7ebb7249de71dd89a85aaf441f</t>
@@ -107,6 +665,531 @@
     <t>818f4584586616243424fbc7eec2be98a6bfec7e</t>
   </si>
   <si>
+    <t>2572366dab98b37f0048bbfeaeb4360bcaa80e77</t>
+  </si>
+  <si>
+    <t>b7c10949c0fcdf5a38c99d0c895ac3954b57e21e</t>
+  </si>
+  <si>
+    <t>b8004bcad043934cada0adeb2731bc304660ec59</t>
+  </si>
+  <si>
+    <t>63335df158e4407d4f211d2e074c66054e98d93c</t>
+  </si>
+  <si>
+    <t>1056ee16236ea0e6b09aa49cef2870a54c2a6434</t>
+  </si>
+  <si>
+    <t>36f118a558b26e65593de12aa7e70f6f03270981</t>
+  </si>
+  <si>
+    <t>5e6d8d29cc42c0dac4c57646b531f9ac25b64f12</t>
+  </si>
+  <si>
+    <t>012d71553f1429f92f35b39645956168748731db</t>
+  </si>
+  <si>
+    <t>e32f486434b80245d06a78728576644cb0d3ce49</t>
+  </si>
+  <si>
+    <t>9a8c2b5af7840a5e41f5ea4c6a6c1298eff1e651</t>
+  </si>
+  <si>
+    <t>a24b2cd7fcf6d6c739783137f87a3c396081f8af</t>
+  </si>
+  <si>
+    <t>28bc1243143107c5480462206ba6fe85f535b8ff</t>
+  </si>
+  <si>
+    <t>b9f3bf3f2f18592d7a2e33dea6774fadbd2b3ea1</t>
+  </si>
+  <si>
+    <t>442f9c7e12f413e6d2c38a777df4574809b65a50</t>
+  </si>
+  <si>
+    <t>937bfd6bebe1445b4ccc2fdceb9919cdacff5923</t>
+  </si>
+  <si>
+    <t>44a1519c76253d4ac09f131a11a51e5856f3c6dd</t>
+  </si>
+  <si>
+    <t>652d62214d79618cac01e39d6e4713fb3ff7f498</t>
+  </si>
+  <si>
+    <t>2701ea45cba10eb3493d60f58101adc466484207</t>
+  </si>
+  <si>
+    <t>cad5364899cf81b3104989f1eb017c2d3f268e40</t>
+  </si>
+  <si>
+    <t>9925f2c2af6b8edb1313c7ae708b45da2115c657</t>
+  </si>
+  <si>
+    <t>37244f98964217b91c14a7a57d00eb0a9030adc0</t>
+  </si>
+  <si>
+    <t>8ec142efb3ed2f1a55f73c210bf2bc167ae4e26e</t>
+  </si>
+  <si>
+    <t>7d431035cabb7066a877963351f8639cab2e9630</t>
+  </si>
+  <si>
+    <t>5673c4c9e04da98eca2d5bb3dfff3e8dbcf33586</t>
+  </si>
+  <si>
+    <t>419fb6956818fbb750d7a8f328e8c2e40659f107</t>
+  </si>
+  <si>
+    <t>25b198b3a61a0eabcb7ae36e676a989b4b4a60a8</t>
+  </si>
+  <si>
+    <t>5015272f27b2efaf1d855d3da3dc777c8c672457</t>
+  </si>
+  <si>
+    <t>7c56e57cd1f19cf661a15e4125820c322e81fda9</t>
+  </si>
+  <si>
+    <t>ca7dd36dade6a2097fc36063e3be8a6275e8018c</t>
+  </si>
+  <si>
+    <t>04f970414ef35eeab8c9773b0dbd1966598d6dbf</t>
+  </si>
+  <si>
+    <t>97fb14314ce1e1e72a94a8f34fca0a4348bbfc78</t>
+  </si>
+  <si>
+    <t>310c2b1590d69cf3cbdb42e4cc8604e697aedac4</t>
+  </si>
+  <si>
+    <t>d96e689fe4c6b15cfd8c4fa8e0bd712bcf1551e0</t>
+  </si>
+  <si>
+    <t>9e3299841772b04dbe3e8f9b26b7d263021c8811</t>
+  </si>
+  <si>
+    <t>aedc87712089b11122ec15c722ffbb90e05872b8</t>
+  </si>
+  <si>
+    <t>14ac5605004d9bbc951ad28b2b0767fcd5a213bb</t>
+  </si>
+  <si>
+    <t>81fd582117a4a6378faeab9998ca801e0838a9ac</t>
+  </si>
+  <si>
+    <t>4bc2a2e5c709281d7b4270efc3b70d92fea48012</t>
+  </si>
+  <si>
+    <t>cd34149dbf9955f020bfc8cde90c0229d4cadb4c</t>
+  </si>
+  <si>
+    <t>88c9d7b551d28edd60cdf9106d99871b69215138</t>
+  </si>
+  <si>
+    <t>87134c78d02462805348d326454ed2fcf1e018a5</t>
+  </si>
+  <si>
+    <t>d63f45c4ff782d0c9b9c9c8e599d5a790b188139</t>
+  </si>
+  <si>
+    <t>c0b09ce81b7d42ea979742e8c2a0bc06d24e1933</t>
+  </si>
+  <si>
+    <t>f218f80a44d342d7b1ba363e98ec9a5a8d09570f</t>
+  </si>
+  <si>
+    <t>0e20990ce8f13e2993f58062f5b79a1062c7fde5</t>
+  </si>
+  <si>
+    <t>9084abb41f5cf6ca740d7211dcb35a1c36eda515</t>
+  </si>
+  <si>
+    <t>b6749f79d45cf64cb6542ff30cf2470bb905d1b6</t>
+  </si>
+  <si>
+    <t>1ea1074ca347645f4cb511d9f6eb4e00e3408406</t>
+  </si>
+  <si>
+    <t>26768450c2bfd96cd67e4c77990550c92b4a8063</t>
+  </si>
+  <si>
+    <t>816bb116f3461c43fe86ae60a678ae0e2d7d73c3</t>
+  </si>
+  <si>
+    <t>cdc348d8380a316bbd5aa0628a9ead27355c0684</t>
+  </si>
+  <si>
+    <t>e96e080094d01c96f6bcf62b2e8604ecfe03c910</t>
+  </si>
+  <si>
+    <t>184a8010089910cc9f486bfeda1bc3d7b00c3fb8</t>
+  </si>
+  <si>
+    <t>20bee624a6e9fa617124030dc8c00694e7087825</t>
+  </si>
+  <si>
+    <t>6a823201df638ebf75a988a6826648bc6e2f25d0</t>
+  </si>
+  <si>
+    <t>d7987f98b6c172a0aa4429a59db96a38729aa6ed</t>
+  </si>
+  <si>
+    <t>372224313ad828a6370724ba959efbebee26482d</t>
+  </si>
+  <si>
+    <t>3596f488136a865d9ed36f85bc9c181c7138b035</t>
+  </si>
+  <si>
+    <t>68edb42c9b13667dffeb41c497c1efc87b4ae276</t>
+  </si>
+  <si>
+    <t>7fd088c808c6c95a31aa0d7751ebc6e29096a8ea</t>
+  </si>
+  <si>
+    <t>f06ab8ebe4ce2e387e570b83428832e4f263b699</t>
+  </si>
+  <si>
+    <t>138bca9f38c4d8b5c3508f07de48b1c0344e1415</t>
+  </si>
+  <si>
+    <t>b108e055d2d8aded739238c3465fcde57e3de7ef</t>
+  </si>
+  <si>
+    <t>448b941198cf05696b9971ac63c7a155e6fe54fa</t>
+  </si>
+  <si>
+    <t>bd915735f299c44eea4fb097885ad395a7430c07</t>
+  </si>
+  <si>
+    <t>8bbab34c6cc9471f239e01442e531c8e688d501b</t>
+  </si>
+  <si>
+    <t>48049a2606c324f3e3ad4f9b1ebf77c52a9e9c87</t>
+  </si>
+  <si>
+    <t>c0aa84911ceec370c33616c3658df16313b8dfde</t>
+  </si>
+  <si>
+    <t>27e448164a23b5a43f24e3fc76ae005a9ccdf2c0</t>
+  </si>
+  <si>
+    <t>c7598257fdad95f25291c71bbbd95daded97551b</t>
+  </si>
+  <si>
+    <t>5c3a7660d7b99e5505d85d5dcaa5b01cba11dfc3</t>
+  </si>
+  <si>
+    <t>9dc37fb384b03dedc7a22cf3fa5f33dab45ff653</t>
+  </si>
+  <si>
+    <t>b9dce6b0f982a5118259d71473f2c959d21af983</t>
+  </si>
+  <si>
+    <t>b40e347490f8413fa062285a301fad3c27cf2d76</t>
+  </si>
+  <si>
+    <t>391cce2b1a3f3c72d8f0493aad7ce39d3e0170ce</t>
+  </si>
+  <si>
+    <t>f89538c24974c821c0fb3380ff11b60d03993f91</t>
+  </si>
+  <si>
+    <t>ef71fa24394c6aefb4a030b79d1f5497273ced8d</t>
+  </si>
+  <si>
+    <t>21a30a8ceae90439e9b4a44d4aedb7ff6cefb34c</t>
+  </si>
+  <si>
+    <t>19000bc52be08fd9148bcb2bce3ee9845aca2e28</t>
+  </si>
+  <si>
+    <t>38f69fe5c98068cf979f00959e07aba10b5a2165</t>
+  </si>
+  <si>
+    <t>6b5a4c10ad3a5b3e38ddeb1edd8d53db227b68c3</t>
+  </si>
+  <si>
+    <t>5e5da1e666812bed68a3cae04dfaa48a1d83eb57</t>
+  </si>
+  <si>
+    <t>57b68c5d9bf9e1ae5c4a518799bdf4dc39e33a29</t>
+  </si>
+  <si>
+    <t>2796ba1fcd929f9ed5133d9064e24aaa392dbe5f</t>
+  </si>
+  <si>
+    <t>d646b5cbbade652f661e0dd96c22e64b04f5f17b</t>
+  </si>
+  <si>
+    <t>f1ee9896581b77ffd9c44d09d5b128fc69815fc9</t>
+  </si>
+  <si>
+    <t>fa8332c52ba2c4ca01fb2c77b13c41ebf2a9d7cb</t>
+  </si>
+  <si>
+    <t>6ed4871bcc39079209b192fd33303096018f9de6</t>
+  </si>
+  <si>
+    <t>46a53cd35f5e8f9e0e4c20b1253ebd1bcb3166f4</t>
+  </si>
+  <si>
+    <t>5aac1faca68b57ac728769e169bee72c3822ba85</t>
+  </si>
+  <si>
+    <t>76e3ae96a10dc650d07531d9821cecf91d88b376</t>
+  </si>
+  <si>
+    <t>ad7507e9770d25601d19f40d39e84f4e5896fe9a</t>
+  </si>
+  <si>
+    <t>b8d6ab8557e22735c1610498a7e761d136ff42e4</t>
+  </si>
+  <si>
+    <t>0c8a46000af2bbc82b5eddaf0edef9e4fddee767</t>
+  </si>
+  <si>
+    <t>f4131678fd5ecc8796697ad86141e6700751ac29</t>
+  </si>
+  <si>
+    <t>34298948003ede00306bc0342949fdaa11cf3365</t>
+  </si>
+  <si>
+    <t>2e1907b432a9f8402db71835ff29f98bdd771674</t>
+  </si>
+  <si>
+    <t>b80aa6d05e0c22d2dd4e849229be9deb31171c4a</t>
+  </si>
+  <si>
+    <t>a7f22bdc0c2b4726ab5dcfb224da674c2f21c56e</t>
+  </si>
+  <si>
+    <t>65ee1acc39a1299beb5c3b1f7a9e55e35d7b729e</t>
+  </si>
+  <si>
+    <t>b7ad940489a12916c5d2ac25387c16fc16fcd4b4</t>
+  </si>
+  <si>
+    <t>905e11f44201176794b097861f379588ccb9aad0</t>
+  </si>
+  <si>
+    <t>51619764a9e10f36757d3c0eeca3e8ff14d3bafa</t>
+  </si>
+  <si>
+    <t>e32b25ad93387e587cec94c311091540dfa8f083</t>
+  </si>
+  <si>
+    <t>9b037d0cece4338f803dda222363571e0c1d97df</t>
+  </si>
+  <si>
+    <t>486acdc633c498d4335711e30817cc70faacc487</t>
+  </si>
+  <si>
+    <t>8c3db73149a7f412e97d682aa019dcbf3a0f6535</t>
+  </si>
+  <si>
+    <t>70f99cf9c40d9ea5b24bf631ff148802960c500c</t>
+  </si>
+  <si>
+    <t>f0a5de29a3250ce479f92736948aa7aa6cfa971a</t>
+  </si>
+  <si>
+    <t>f597c16e47ea989db7b037b34f880b8543ca8bb6</t>
+  </si>
+  <si>
+    <t>792ca819bac2c78c61bc5cbfee66f4ec28e313ee</t>
+  </si>
+  <si>
+    <t>7fa6bb57bd280b432881467d2c4d80c341044981</t>
+  </si>
+  <si>
+    <t>ef5849d7a45ef41ff64ed440eb09e44a4bc8a840</t>
+  </si>
+  <si>
+    <t>08f47917e07573b372c413ff1bd33b0bdd0d0f67</t>
+  </si>
+  <si>
+    <t>36bb402d79e259e8739ece5bc005c06ec8f363e9</t>
+  </si>
+  <si>
+    <t>8b854239d3dac1ce669419cb82cfcc45e32e4752</t>
+  </si>
+  <si>
+    <t>2df66e1b6d2413afe632d176cdf093cd2936b56e</t>
+  </si>
+  <si>
+    <t>e9ed076bec0f3853458989c68f9bfc34e0199de1</t>
+  </si>
+  <si>
+    <t>fc379cf06e913be501e2115754129af66fe67be0</t>
+  </si>
+  <si>
+    <t>39aafa98c74c853e40dc6a4362ea13a628e865b6</t>
+  </si>
+  <si>
+    <t>786aeb778c4e3e91166f03d005530902db219577</t>
+  </si>
+  <si>
+    <t>f44e6c7f891ff4c528f681f5157b520c9982e91d</t>
+  </si>
+  <si>
+    <t>2a0d8e94c6df8b0e94aad5b8e0d9b9191ec08bc8</t>
+  </si>
+  <si>
+    <t>4aa3dd4b847e747387475e9249c4aba97b6ef8ac</t>
+  </si>
+  <si>
+    <t>8f716803a364365c7bee890e3f99f7a5a1053e67</t>
+  </si>
+  <si>
+    <t>cd69a662535ebdd0d572379076030476f5d11794</t>
+  </si>
+  <si>
+    <t>ab15c1bcf3e05bc843c1d7d509ef43a45e70459d</t>
+  </si>
+  <si>
+    <t>096d1833d55356ee8293399c180aba8e05bec9cf</t>
+  </si>
+  <si>
+    <t>e00853fe721093b6fba059e0107ecfe7d9f911c9</t>
+  </si>
+  <si>
+    <t>f8b4e8a6ef7ce87fccee3ad0c2e5d0d7927b6870</t>
+  </si>
+  <si>
+    <t>eac238ed3ff270de523eea38a440b8780f59e0f7</t>
+  </si>
+  <si>
+    <t>6fdcab0b7ed486cb055195443311bffd65b099de</t>
+  </si>
+  <si>
+    <t>eca873299bef401bbca4c7084dc790063446e986</t>
+  </si>
+  <si>
+    <t>6aed7cf0cf3bfa5385c47fa5a3ed7e7804d3bf66</t>
+  </si>
+  <si>
+    <t>2d9e1206d440c107ff07b9b64598383bb245a472</t>
+  </si>
+  <si>
+    <t>bea887da6487c06c834e5512ea1db893754c6865</t>
+  </si>
+  <si>
+    <t>2bbdda7e5705c488b0e3c4cc9aec82f602737309</t>
+  </si>
+  <si>
+    <t>a00464dad1199b6a4c36d6b6c1de0d3903865258</t>
+  </si>
+  <si>
+    <t>c09b62024e020bf344b13b934f36921c19766d5b</t>
+  </si>
+  <si>
+    <t>1b17bc988c7aec46eb98392c8aa23bf54f62cba9</t>
+  </si>
+  <si>
+    <t>b5859aaad0668a673328ebb9dc00e478f04c7f86</t>
+  </si>
+  <si>
+    <t>a8c8c579d0ab24901d6e81cf52cc0b12efaabcec</t>
+  </si>
+  <si>
+    <t>2ac1eba6584a0af546849261cd2ecf31d1e9e9b5</t>
+  </si>
+  <si>
+    <t>6e5147c6c886846d6415b7b303c8181ac0170c9d</t>
+  </si>
+  <si>
+    <t>17ba34ce380ab8fbe3c40e75f7e21f85383b4a9f</t>
+  </si>
+  <si>
+    <t>5a280d042b15474c3c9d3a2c2415c76449eb7bbe</t>
+  </si>
+  <si>
+    <t>a3bf2290ee30948f0b4d88c83dbae6dcbec3dc1d</t>
+  </si>
+  <si>
+    <t>4e29f6227d0c89ace46a005504d702aee9f78547</t>
+  </si>
+  <si>
+    <t>e0dbc3f891a483deeecbbd9e019f76fef89447f7</t>
+  </si>
+  <si>
+    <t>f232352a2953d9e9ddbe8c99dad34145d9449bf9</t>
+  </si>
+  <si>
+    <t>2b3ba7361fcb43363737008aa79f37dfa0fd1469</t>
+  </si>
+  <si>
+    <t>86beb8eeb9fa2f7ec1f1ef5878598a76f7648ab9</t>
+  </si>
+  <si>
+    <t>189ffbe56c828d68473467e54fcb7a9e38ccb701</t>
+  </si>
+  <si>
+    <t>29ea7b771b34959d34324bdcda541fe22065ac8d</t>
+  </si>
+  <si>
+    <t>e5c3d4a1698526115dfae6da3c22760bce464ec6</t>
+  </si>
+  <si>
+    <t>50b8d043c3c4268c84dd77fecbb4608fb89da0e8</t>
+  </si>
+  <si>
+    <t>778deebea6f56c3e6862a3bdd827855e3cd563ef</t>
+  </si>
+  <si>
+    <t>8eb9b52c46b86820e1d3516ef299ae9b14f38acf</t>
+  </si>
+  <si>
+    <t>6950b31110974ac3c04026bf682843e3741e04f0</t>
+  </si>
+  <si>
+    <t>7cff60b8f7c5bb85df91572317b4b5bd51bc6f95</t>
+  </si>
+  <si>
+    <t>469f44270c1f37e6fe16bc324fea487a6354679a</t>
+  </si>
+  <si>
+    <t>733382ed32219726f1e795ac831c6736068c3e9f</t>
+  </si>
+  <si>
+    <t>4e5e4180d5945cfd88076466074968f9871edf62</t>
+  </si>
+  <si>
+    <t>11a2562ad9d13daa42651efcf759882ab7d62a72</t>
+  </si>
+  <si>
+    <t>30315ec382303d1a7e0b33863cc954448fbf027e</t>
+  </si>
+  <si>
+    <t>519067d8270ceaf7ad62deab1adeb124bafefcd1</t>
+  </si>
+  <si>
+    <t>d031feab45a09aa6bb3444c09ea38f12276e4c24</t>
+  </si>
+  <si>
+    <t>8fd5cd7e2c5fb314f71559717982982b06116f96</t>
+  </si>
+  <si>
+    <t>659c342e2d51b22a224979b66b1f0dfd37725eeb</t>
+  </si>
+  <si>
+    <t>f791dfba36282cb8bb0e95af2d173c373080a1ad</t>
+  </si>
+  <si>
+    <t>0024e0179a40a1b659bdb817ce24b8988f96902e</t>
+  </si>
+  <si>
+    <t>041ec460fff291251dec659a19eec5976be32c91</t>
+  </si>
+  <si>
+    <t>5c12cf16ea29aac0969bf4bf3ac2cc14ad48fd51</t>
+  </si>
+  <si>
+    <t>60ab32a6b4b0fa575a972fe8a0e17cf14d8f23f8</t>
+  </si>
+  <si>
+    <t>03b3ff761090d432d5f57446cfeb0d8f7651696d</t>
+  </si>
+  <si>
     <t>4e9c357464e4602510c6696e841c01f85e2966db</t>
   </si>
   <si>
@@ -132,6 +1215,24 @@
   </si>
   <si>
     <t>9b585e22bed27bb2f5267141a0e23f288e07ab3b</t>
+  </si>
+  <si>
+    <t>f7dc6062c2a9d1ad95d94bbd940ad6794531a9f3</t>
+  </si>
+  <si>
+    <t>3cfc5fe311b72e56e52a79a5787faf9d0e277299</t>
+  </si>
+  <si>
+    <t>913fa0c37c8a5416ecc638bcbf52436d9a9fbc62</t>
+  </si>
+  <si>
+    <t>b3cdb50136ec55e2cca902a28827a53e7d2d238d</t>
+  </si>
+  <si>
+    <t>e74daf8b1ee10a709bc7db117cdcc60ddfe3b41d</t>
+  </si>
+  <si>
+    <t>f8935b01861e587ad1ee0e6d7f7034065ad9ac2d</t>
   </si>
 </sst>
 </file>
@@ -176,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -222,13 +1323,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>42.0</v>
+        <v>280.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -237,10 +1338,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.38999998569488525</v>
+        <v>7.434999942779541</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -254,13 +1355,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>26.0</v>
+        <v>285.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -269,10 +1370,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>0.13300000131130219</v>
+        <v>5.405999660491943</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -286,13 +1387,13 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>25.0</v>
+        <v>42.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G4" t="b" s="0">
         <v>0</v>
@@ -301,10 +1402,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>0.09700001031160355</v>
+        <v>1.3619999885559082</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -318,13 +1419,13 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>4.0</v>
+        <v>288.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G5" t="b" s="0">
         <v>0</v>
@@ -333,10 +1434,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>0.050999999046325684</v>
+        <v>5.5279998779296875</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -350,25 +1451,25 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>80.0</v>
+        <v>384.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="G6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>66.79800415039062</v>
+        <v>6.57499885559082</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -376,45 +1477,45 @@
         <v>25</v>
       </c>
       <c r="B7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="C7" t="s" s="0">
-        <v>27</v>
-      </c>
       <c r="D7" t="n" s="0">
-        <v>76.0</v>
+        <v>287.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="G7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>65.52799987792969</v>
+        <v>5.695999622344971</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="C8" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="C8" t="s" s="0">
-        <v>30</v>
-      </c>
       <c r="D8" t="n" s="0">
-        <v>10.0</v>
+        <v>282.0</v>
       </c>
       <c r="E8" t="n" s="0">
         <v>1.0</v>
@@ -429,30 +1530,30 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>0.18800000846385956</v>
+        <v>5.490000247955322</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="C9" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C9" t="s" s="0">
-        <v>33</v>
-      </c>
       <c r="D9" t="n" s="0">
-        <v>163.0</v>
+        <v>332.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" t="b" s="0">
         <v>0</v>
@@ -461,30 +1562,30 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>67.78399658203125</v>
+        <v>5.278999328613281</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="C10" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="C10" t="s" s="0">
-        <v>36</v>
-      </c>
       <c r="D10" t="n" s="0">
-        <v>163.0</v>
+        <v>395.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G10" t="b" s="0">
         <v>0</v>
@@ -493,42 +1594,4138 @@
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>71.26000213623047</v>
+        <v>35.07899475097656</v>
       </c>
       <c r="J10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="C11" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="C11" t="s" s="0">
+      <c r="D11" t="n" s="0">
+        <v>119.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>30.899999618530273</v>
+      </c>
+      <c r="J11" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="D11" t="n" s="0">
-        <v>163.0</v>
-      </c>
-      <c r="E11" t="n" s="0">
+      <c r="B12" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="D12" t="n" s="0">
+        <v>119.0</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G12" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>30.62099838256836</v>
+      </c>
+      <c r="J12" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D13" t="n" s="0">
+        <v>259.0</v>
+      </c>
+      <c r="E13" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G13" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>51.35799789428711</v>
+      </c>
+      <c r="J13" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="D14" t="n" s="0">
+        <v>134.0</v>
+      </c>
+      <c r="E14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G14" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>33.597999572753906</v>
+      </c>
+      <c r="J14" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="D15" t="n" s="0">
+        <v>131.0</v>
+      </c>
+      <c r="E15" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F15" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G15" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>33.7650032043457</v>
+      </c>
+      <c r="J15" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="D16" t="n" s="0">
+        <v>173.0</v>
+      </c>
+      <c r="E16" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F16" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G16" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>44.615997314453125</v>
+      </c>
+      <c r="J16" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="D17" t="n" s="0">
+        <v>393.0</v>
+      </c>
+      <c r="E17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G17" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>73.80299377441406</v>
+      </c>
+      <c r="J17" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="D18" t="n" s="0">
+        <v>172.0</v>
+      </c>
+      <c r="E18" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F18" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G18" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>42.68199920654297</v>
+      </c>
+      <c r="J18" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="D19" t="n" s="0">
+        <v>131.0</v>
+      </c>
+      <c r="E19" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F19" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G19" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>34.69599914550781</v>
+      </c>
+      <c r="J19" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="D20" t="n" s="0">
+        <v>403.0</v>
+      </c>
+      <c r="E20" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F20" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G20" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>76.14600372314453</v>
+      </c>
+      <c r="J20" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="D21" t="n" s="0">
+        <v>398.0</v>
+      </c>
+      <c r="E21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G21" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>74.35000610351562</v>
+      </c>
+      <c r="J21" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="D22" t="n" s="0">
+        <v>58.0</v>
+      </c>
+      <c r="E22" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="F22" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G22" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>66.10800170898438</v>
+      </c>
+      <c r="J22" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D23" t="n" s="0">
+        <v>131.0</v>
+      </c>
+      <c r="E23" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F23" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G23" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n" s="0">
+        <v>39.20800018310547</v>
+      </c>
+      <c r="J23" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="D24" t="n" s="0">
+        <v>62.0</v>
+      </c>
+      <c r="E24" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="F24" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G24" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n" s="0">
+        <v>66.8800048828125</v>
+      </c>
+      <c r="J24" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D25" t="n" s="0">
+        <v>144.0</v>
+      </c>
+      <c r="E25" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F25" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G25" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n" s="0">
+        <v>32.567996978759766</v>
+      </c>
+      <c r="J25" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="D26" t="n" s="0">
+        <v>396.0</v>
+      </c>
+      <c r="E26" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F26" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G26" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n" s="0">
+        <v>76.91100311279297</v>
+      </c>
+      <c r="J26" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="D27" t="n" s="0">
+        <v>36.0</v>
+      </c>
+      <c r="E27" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F27" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G27" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n" s="0">
+        <v>0.3749999701976776</v>
+      </c>
+      <c r="J27" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="D28" t="n" s="0">
+        <v>114.0</v>
+      </c>
+      <c r="E28" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F28" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G28" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n" s="0">
+        <v>17.676998138427734</v>
+      </c>
+      <c r="J28" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="D29" t="n" s="0">
+        <v>53.0</v>
+      </c>
+      <c r="E29" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F29" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G29" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n" s="0">
+        <v>6.947999954223633</v>
+      </c>
+      <c r="J29" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D30" t="n" s="0">
+        <v>176.0</v>
+      </c>
+      <c r="E30" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F30" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G30" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n" s="0">
+        <v>0.4869999885559082</v>
+      </c>
+      <c r="J30" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="D31" t="n" s="0">
+        <v>35.0</v>
+      </c>
+      <c r="E31" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F31" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G31" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n" s="0">
+        <v>0.5509999394416809</v>
+      </c>
+      <c r="J31" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="D32" t="n" s="0">
+        <v>330.0</v>
+      </c>
+      <c r="E32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G32" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n" s="0">
+        <v>88.21299743652344</v>
+      </c>
+      <c r="J32" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="D33" t="n" s="0">
+        <v>310.0</v>
+      </c>
+      <c r="E33" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F33" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G33" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n" s="0">
+        <v>86.593994140625</v>
+      </c>
+      <c r="J33" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="D34" t="n" s="0">
+        <v>62.0</v>
+      </c>
+      <c r="E34" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="F34" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="G34" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n" s="0">
+        <v>5.456999778747559</v>
+      </c>
+      <c r="J34" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="D35" t="n" s="0">
+        <v>62.0</v>
+      </c>
+      <c r="E35" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F35" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G35" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n" s="0">
+        <v>4.223000526428223</v>
+      </c>
+      <c r="J35" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="D36" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E36" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F36" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G36" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n" s="0">
+        <v>2.01200008392334</v>
+      </c>
+      <c r="J36" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="D37" t="n" s="0">
+        <v>136.0</v>
+      </c>
+      <c r="E37" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F37" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G37" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n" s="0">
+        <v>60.76699447631836</v>
+      </c>
+      <c r="J37" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="D38" t="n" s="0">
+        <v>136.0</v>
+      </c>
+      <c r="E38" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F38" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G38" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n" s="0">
+        <v>62.7449951171875</v>
+      </c>
+      <c r="J38" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="D39" t="n" s="0">
+        <v>136.0</v>
+      </c>
+      <c r="E39" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F39" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G39" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n" s="0">
+        <v>63.067996978759766</v>
+      </c>
+      <c r="J39" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="D40" t="n" s="0">
+        <v>108.0</v>
+      </c>
+      <c r="E40" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F40" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G40" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n" s="0">
+        <v>60.73600387573242</v>
+      </c>
+      <c r="J40" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="D41" t="n" s="0">
+        <v>108.0</v>
+      </c>
+      <c r="E41" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F41" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G41" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H41" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n" s="0">
+        <v>62.25099563598633</v>
+      </c>
+      <c r="J41" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="D42" t="n" s="0">
+        <v>108.0</v>
+      </c>
+      <c r="E42" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F42" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G42" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H42" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n" s="0">
+        <v>59.09499740600586</v>
+      </c>
+      <c r="J42" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="D43" t="n" s="0">
+        <v>136.0</v>
+      </c>
+      <c r="E43" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F43" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G43" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H43" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n" s="0">
+        <v>62.194007873535156</v>
+      </c>
+      <c r="J43" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="D44" t="n" s="0">
+        <v>64.0</v>
+      </c>
+      <c r="E44" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F44" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G44" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H44" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n" s="0">
+        <v>7.8379998207092285</v>
+      </c>
+      <c r="J44" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="D45" t="n" s="0">
+        <v>64.0</v>
+      </c>
+      <c r="E45" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F45" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G45" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H45" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n" s="0">
+        <v>9.177000999450684</v>
+      </c>
+      <c r="J45" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="D46" t="n" s="0">
+        <v>64.0</v>
+      </c>
+      <c r="E46" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F46" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G46" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H46" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n" s="0">
+        <v>9.128000259399414</v>
+      </c>
+      <c r="J46" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="D47" t="n" s="0">
+        <v>63.0</v>
+      </c>
+      <c r="E47" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F47" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G47" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H47" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n" s="0">
+        <v>7.835000038146973</v>
+      </c>
+      <c r="J47" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="D48" t="n" s="0">
+        <v>63.0</v>
+      </c>
+      <c r="E48" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F48" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G48" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H48" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n" s="0">
+        <v>9.193000793457031</v>
+      </c>
+      <c r="J48" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="D49" t="n" s="0">
+        <v>37.0</v>
+      </c>
+      <c r="E49" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F49" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G49" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H49" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n" s="0">
+        <v>105.90901184082031</v>
+      </c>
+      <c r="J49" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="D50" t="n" s="0">
+        <v>63.0</v>
+      </c>
+      <c r="E50" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F50" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G50" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n" s="0">
+        <v>10.316999435424805</v>
+      </c>
+      <c r="J50" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="D51" t="n" s="0">
+        <v>63.0</v>
+      </c>
+      <c r="E51" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F51" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G51" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H51" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n" s="0">
+        <v>10.609000205993652</v>
+      </c>
+      <c r="J51" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="D52" t="n" s="0">
+        <v>63.0</v>
+      </c>
+      <c r="E52" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F52" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G52" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H52" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n" s="0">
+        <v>10.545000076293945</v>
+      </c>
+      <c r="J52" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="D53" t="n" s="0">
+        <v>37.0</v>
+      </c>
+      <c r="E53" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F53" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G53" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H53" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n" s="0">
+        <v>106.48600006103516</v>
+      </c>
+      <c r="J53" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="D54" t="n" s="0">
+        <v>63.0</v>
+      </c>
+      <c r="E54" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F54" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G54" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H54" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n" s="0">
+        <v>8.173999786376953</v>
+      </c>
+      <c r="J54" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="D55" t="n" s="0">
+        <v>32.0</v>
+      </c>
+      <c r="E55" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F55" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G55" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H55" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n" s="0">
+        <v>6.236000061035156</v>
+      </c>
+      <c r="J55" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="D56" t="n" s="0">
+        <v>63.0</v>
+      </c>
+      <c r="E56" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F56" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G56" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H56" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n" s="0">
+        <v>12.164000511169434</v>
+      </c>
+      <c r="J56" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="D57" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E57" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F57" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G57" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H57" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n" s="0">
+        <v>1.559000015258789</v>
+      </c>
+      <c r="J57" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="D58" t="n" s="0">
+        <v>32.0</v>
+      </c>
+      <c r="E58" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F58" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G58" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H58" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n" s="0">
+        <v>8.461000442504883</v>
+      </c>
+      <c r="J58" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="D59" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E59" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F59" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G59" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n" s="0">
+        <v>3.61899995803833</v>
+      </c>
+      <c r="J59" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="D60" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E60" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F60" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G60" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H60" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n" s="0">
+        <v>3.0290000438690186</v>
+      </c>
+      <c r="J60" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="D61" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E61" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F61" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G61" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n" s="0">
+        <v>2.367000102996826</v>
+      </c>
+      <c r="J61" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="D62" t="n" s="0">
+        <v>44.0</v>
+      </c>
+      <c r="E62" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="F62" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="G62" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H62" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n" s="0">
+        <v>91.4949951171875</v>
+      </c>
+      <c r="J62" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="D63" t="n" s="0">
+        <v>114.0</v>
+      </c>
+      <c r="E63" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F63" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G63" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H63" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n" s="0">
+        <v>19.659997940063477</v>
+      </c>
+      <c r="J63" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>193</v>
+      </c>
+      <c r="D64" t="n" s="0">
+        <v>44.0</v>
+      </c>
+      <c r="E64" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F64" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G64" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H64" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n" s="0">
+        <v>94.48200988769531</v>
+      </c>
+      <c r="J64" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="D65" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E65" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F65" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G65" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H65" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n" s="0">
+        <v>4.629000186920166</v>
+      </c>
+      <c r="J65" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="D66" t="n" s="0">
+        <v>125.0</v>
+      </c>
+      <c r="E66" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="F66" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="G66" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H66" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n" s="0">
+        <v>28.081005096435547</v>
+      </c>
+      <c r="J66" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="D67" t="n" s="0">
+        <v>41.0</v>
+      </c>
+      <c r="E67" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F67" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G67" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H67" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n" s="0">
+        <v>113.83499908447266</v>
+      </c>
+      <c r="J67" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="D68" t="n" s="0">
+        <v>110.0</v>
+      </c>
+      <c r="E68" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F68" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G68" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H68" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n" s="0">
+        <v>21.260997772216797</v>
+      </c>
+      <c r="J68" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="D69" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E69" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="F69" t="n" s="0">
         <v>11.0</v>
       </c>
-      <c r="F11" t="n" s="0">
+      <c r="G69" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H69" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n" s="0">
+        <v>4.065999984741211</v>
+      </c>
+      <c r="J69" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="D70" t="n" s="0">
+        <v>42.0</v>
+      </c>
+      <c r="E70" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F70" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G70" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H70" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n" s="0">
+        <v>11.631999015808105</v>
+      </c>
+      <c r="J70" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="D71" t="n" s="0">
+        <v>128.0</v>
+      </c>
+      <c r="E71" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F71" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G71" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H71" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n" s="0">
+        <v>144.48399353027344</v>
+      </c>
+      <c r="J71" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="D72" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E72" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F72" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G72" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H72" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n" s="0">
+        <v>4.700000286102295</v>
+      </c>
+      <c r="J72" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="D73" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E73" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F73" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G73" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H73" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n" s="0">
+        <v>3.922999858856201</v>
+      </c>
+      <c r="J73" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="D74" t="n" s="0">
+        <v>110.0</v>
+      </c>
+      <c r="E74" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F74" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G74" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H74" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n" s="0">
+        <v>21.49799919128418</v>
+      </c>
+      <c r="J74" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="D75" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E75" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F75" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G75" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H75" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n" s="0">
+        <v>4.233999729156494</v>
+      </c>
+      <c r="J75" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>227</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="D76" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E76" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="F76" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="G76" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H76" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n" s="0">
+        <v>4.409000396728516</v>
+      </c>
+      <c r="J76" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="D77" t="n" s="0">
+        <v>42.0</v>
+      </c>
+      <c r="E77" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F77" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G77" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H77" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n" s="0">
+        <v>9.793999671936035</v>
+      </c>
+      <c r="J77" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="D78" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E78" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F78" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G78" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H78" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n" s="0">
+        <v>1.9769999980926514</v>
+      </c>
+      <c r="J78" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>235</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="D79" t="n" s="0">
+        <v>42.0</v>
+      </c>
+      <c r="E79" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="F79" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="G79" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H79" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n" s="0">
+        <v>6.3580002784729</v>
+      </c>
+      <c r="J79" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>237</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>238</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>239</v>
+      </c>
+      <c r="D80" t="n" s="0">
+        <v>110.0</v>
+      </c>
+      <c r="E80" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F80" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G80" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H80" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n" s="0">
+        <v>18.76799774169922</v>
+      </c>
+      <c r="J80" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="D81" t="n" s="0">
+        <v>110.0</v>
+      </c>
+      <c r="E81" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F81" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G81" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H81" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n" s="0">
+        <v>21.251998901367188</v>
+      </c>
+      <c r="J81" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="D82" t="n" s="0">
+        <v>128.0</v>
+      </c>
+      <c r="E82" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F82" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G82" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H82" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n" s="0">
+        <v>151.56996154785156</v>
+      </c>
+      <c r="J82" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="C83" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="D83" t="n" s="0">
+        <v>128.0</v>
+      </c>
+      <c r="E83" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F83" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G83" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H83" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n" s="0">
+        <v>159.03297424316406</v>
+      </c>
+      <c r="J83" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="D84" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E84" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F84" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G84" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H84" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n" s="0">
+        <v>2.300999879837036</v>
+      </c>
+      <c r="J84" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="C85" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E85" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F85" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G85" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H85" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n" s="0">
+        <v>5.071000099182129</v>
+      </c>
+      <c r="J85" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>255</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="C86" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E86" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F86" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G86" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H86" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n" s="0">
+        <v>2.564000129699707</v>
+      </c>
+      <c r="J86" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="C87" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E87" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F87" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G87" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H87" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n" s="0">
+        <v>4.61199951171875</v>
+      </c>
+      <c r="J87" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E88" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F88" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G88" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H88" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n" s="0">
+        <v>4.3420000076293945</v>
+      </c>
+      <c r="J88" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="C89" t="s" s="0">
+        <v>265</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E89" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F89" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G89" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H89" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n" s="0">
+        <v>3.6730000972747803</v>
+      </c>
+      <c r="J89" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="C90" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="D90" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E90" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F90" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G90" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H90" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I90" t="n" s="0">
+        <v>4.054000377655029</v>
+      </c>
+      <c r="J90" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>269</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>270</v>
+      </c>
+      <c r="C91" t="s" s="0">
+        <v>271</v>
+      </c>
+      <c r="D91" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E91" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F91" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G91" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H91" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I91" t="n" s="0">
+        <v>3.1510000228881836</v>
+      </c>
+      <c r="J91" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>273</v>
+      </c>
+      <c r="C92" t="s" s="0">
+        <v>274</v>
+      </c>
+      <c r="D92" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E92" t="n" s="0">
+        <v>133.0</v>
+      </c>
+      <c r="F92" t="n" s="0">
+        <v>32.0</v>
+      </c>
+      <c r="G92" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H92" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n" s="0">
+        <v>2.823000192642212</v>
+      </c>
+      <c r="J92" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>275</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="C93" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="D93" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E93" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F93" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G93" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H93" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n" s="0">
+        <v>4.063000202178955</v>
+      </c>
+      <c r="J93" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>274</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>278</v>
+      </c>
+      <c r="C94" t="s" s="0">
+        <v>279</v>
+      </c>
+      <c r="D94" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E94" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="F94" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G94" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H94" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I94" t="n" s="0">
+        <v>3.0869998931884766</v>
+      </c>
+      <c r="J94" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="C95" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="D95" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E95" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F95" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G95" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H95" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n" s="0">
+        <v>3.7029998302459717</v>
+      </c>
+      <c r="J95" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="C96" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="D96" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E96" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="F96" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="G96" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H96" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n" s="0">
+        <v>4.2729997634887695</v>
+      </c>
+      <c r="J96" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>285</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>286</v>
+      </c>
+      <c r="C97" t="s" s="0">
+        <v>287</v>
+      </c>
+      <c r="D97" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E97" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F97" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G97" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H97" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n" s="0">
+        <v>2.436000108718872</v>
+      </c>
+      <c r="J97" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>288</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="C98" t="s" s="0">
+        <v>290</v>
+      </c>
+      <c r="D98" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E98" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F98" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G98" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H98" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n" s="0">
+        <v>3.1369998455047607</v>
+      </c>
+      <c r="J98" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>291</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>292</v>
+      </c>
+      <c r="C99" t="s" s="0">
+        <v>293</v>
+      </c>
+      <c r="D99" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E99" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F99" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G99" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H99" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n" s="0">
+        <v>2.8020002841949463</v>
+      </c>
+      <c r="J99" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>294</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>295</v>
+      </c>
+      <c r="C100" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D100" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E100" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F100" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G100" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H100" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I100" t="n" s="0">
+        <v>1.8709999322891235</v>
+      </c>
+      <c r="J100" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>297</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>298</v>
+      </c>
+      <c r="C101" t="s" s="0">
+        <v>299</v>
+      </c>
+      <c r="D101" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E101" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F101" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G101" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H101" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I101" t="n" s="0">
+        <v>2.322999954223633</v>
+      </c>
+      <c r="J101" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>292</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>300</v>
+      </c>
+      <c r="C102" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="D102" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E102" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F102" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G102" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H102" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n" s="0">
+        <v>3.126999855041504</v>
+      </c>
+      <c r="J102" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B103" t="s" s="0">
+        <v>303</v>
+      </c>
+      <c r="C103" t="s" s="0">
+        <v>304</v>
+      </c>
+      <c r="D103" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E103" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F103" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G103" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H103" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I103" t="n" s="0">
+        <v>2.263000011444092</v>
+      </c>
+      <c r="J103" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>305</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>306</v>
+      </c>
+      <c r="C104" t="s" s="0">
+        <v>307</v>
+      </c>
+      <c r="D104" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E104" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F104" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G104" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H104" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I104" t="n" s="0">
+        <v>3.124000072479248</v>
+      </c>
+      <c r="J104" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>308</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>309</v>
+      </c>
+      <c r="C105" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="D105" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E105" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F105" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G105" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H105" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I105" t="n" s="0">
+        <v>2.8480000495910645</v>
+      </c>
+      <c r="J105" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>311</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>312</v>
+      </c>
+      <c r="C106" t="s" s="0">
+        <v>313</v>
+      </c>
+      <c r="D106" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E106" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F106" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G106" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H106" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n" s="0">
+        <v>1.9169999361038208</v>
+      </c>
+      <c r="J106" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>314</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>315</v>
+      </c>
+      <c r="C107" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="D107" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E107" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F107" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G107" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H107" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I107" t="n" s="0">
+        <v>3.246000051498413</v>
+      </c>
+      <c r="J107" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>317</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>318</v>
+      </c>
+      <c r="C108" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="D108" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E108" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="F108" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="G108" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H108" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I108" t="n" s="0">
+        <v>3.320000171661377</v>
+      </c>
+      <c r="J108" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>320</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>321</v>
+      </c>
+      <c r="C109" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="D109" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E109" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="F109" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="G109" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H109" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n" s="0">
+        <v>3.569000005722046</v>
+      </c>
+      <c r="J109" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>323</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="C110" t="s" s="0">
+        <v>325</v>
+      </c>
+      <c r="D110" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E110" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F110" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G110" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H110" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I110" t="n" s="0">
+        <v>3.1660001277923584</v>
+      </c>
+      <c r="J110" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>326</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>327</v>
+      </c>
+      <c r="C111" t="s" s="0">
+        <v>328</v>
+      </c>
+      <c r="D111" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E111" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F111" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G111" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H111" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I111" t="n" s="0">
+        <v>2.484999895095825</v>
+      </c>
+      <c r="J111" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>329</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C112" t="s" s="0">
+        <v>331</v>
+      </c>
+      <c r="D112" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E112" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F112" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G112" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H112" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I112" t="n" s="0">
+        <v>1.790000081062317</v>
+      </c>
+      <c r="J112" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>332</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>333</v>
+      </c>
+      <c r="C113" t="s" s="0">
+        <v>334</v>
+      </c>
+      <c r="D113" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E113" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F113" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G113" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H113" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I113" t="n" s="0">
+        <v>4.144000053405762</v>
+      </c>
+      <c r="J113" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>335</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>336</v>
+      </c>
+      <c r="C114" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="D114" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E114" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F114" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G114" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H114" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I114" t="n" s="0">
+        <v>2.6690001487731934</v>
+      </c>
+      <c r="J114" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>338</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>339</v>
+      </c>
+      <c r="C115" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="D115" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E115" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="F115" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G115" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H115" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I115" t="n" s="0">
+        <v>3.63100004196167</v>
+      </c>
+      <c r="J115" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>342</v>
+      </c>
+      <c r="C116" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="D116" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E116" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F116" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G116" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H116" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n" s="0">
+        <v>2.7850000858306885</v>
+      </c>
+      <c r="J116" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>344</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>345</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>346</v>
+      </c>
+      <c r="D117" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E117" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F117" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G117" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H117" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I117" t="n" s="0">
+        <v>2.484999895095825</v>
+      </c>
+      <c r="J117" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>347</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="C118" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="D118" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E118" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="F118" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="G118" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H118" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I118" t="n" s="0">
+        <v>0.9399999976158142</v>
+      </c>
+      <c r="J118" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>350</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>351</v>
+      </c>
+      <c r="C119" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="D119" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E119" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F119" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G119" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H119" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I119" t="n" s="0">
+        <v>0.7230000495910645</v>
+      </c>
+      <c r="J119" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>353</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="C120" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="D120" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E120" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F120" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G120" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H120" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I120" t="n" s="0">
+        <v>1.7089999914169312</v>
+      </c>
+      <c r="J120" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="D121" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E121" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F121" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G121" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H121" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n" s="0">
+        <v>1.4449999332427979</v>
+      </c>
+      <c r="J121" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="C122" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="D122" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E122" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F122" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G122" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H122" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I122" t="n" s="0">
+        <v>1.1470000743865967</v>
+      </c>
+      <c r="J122" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>362</v>
+      </c>
+      <c r="C123" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="D123" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E123" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F123" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G123" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H123" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I123" t="n" s="0">
+        <v>0.9580000042915344</v>
+      </c>
+      <c r="J123" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>353</v>
+      </c>
+      <c r="C124" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="D124" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E124" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F124" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G124" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H124" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I124" t="n" s="0">
+        <v>1.5519999265670776</v>
+      </c>
+      <c r="J124" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>367</v>
+      </c>
+      <c r="C125" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="D125" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E125" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F125" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G125" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H125" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I125" t="n" s="0">
+        <v>0.9129999279975891</v>
+      </c>
+      <c r="J125" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="C126" t="s" s="0">
+        <v>371</v>
+      </c>
+      <c r="D126" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E126" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F126" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G126" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H126" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n" s="0">
+        <v>1.8839999437332153</v>
+      </c>
+      <c r="J126" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>373</v>
+      </c>
+      <c r="C127" t="s" s="0">
+        <v>374</v>
+      </c>
+      <c r="D127" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E127" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F127" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G127" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H127" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I127" t="n" s="0">
+        <v>1.1670000553131104</v>
+      </c>
+      <c r="J127" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>375</v>
+      </c>
+      <c r="C128" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="D128" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E128" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F128" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G128" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H128" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n" s="0">
+        <v>1.281999945640564</v>
+      </c>
+      <c r="J128" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>375</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="C129" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="D129" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E129" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="F129" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G129" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H129" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I129" t="n" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="J129" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>378</v>
+      </c>
+      <c r="B130" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="C130" t="s" s="0">
+        <v>380</v>
+      </c>
+      <c r="D130" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E130" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F130" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G130" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H130" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I130" t="n" s="0">
+        <v>0.7839999794960022</v>
+      </c>
+      <c r="J130" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>381</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>382</v>
+      </c>
+      <c r="C131" t="s" s="0">
+        <v>383</v>
+      </c>
+      <c r="D131" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E131" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F131" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G131" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H131" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I131" t="n" s="0">
+        <v>0.9160000085830688</v>
+      </c>
+      <c r="J131" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>384</v>
+      </c>
+      <c r="B132" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="C132" t="s" s="0">
+        <v>380</v>
+      </c>
+      <c r="D132" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E132" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F132" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G132" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H132" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n" s="0">
+        <v>0.875</v>
+      </c>
+      <c r="J132" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>386</v>
+      </c>
+      <c r="B133" t="s" s="0">
+        <v>387</v>
+      </c>
+      <c r="C133" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="D133" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E133" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F133" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G133" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H133" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I133" t="n" s="0">
+        <v>0.6430000066757202</v>
+      </c>
+      <c r="J133" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>389</v>
+      </c>
+      <c r="B134" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="C134" t="s" s="0">
+        <v>391</v>
+      </c>
+      <c r="D134" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E134" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="F134" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="G134" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H134" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n" s="0">
+        <v>0.6800000071525574</v>
+      </c>
+      <c r="J134" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="B135" t="s" s="0">
+        <v>393</v>
+      </c>
+      <c r="C135" t="s" s="0">
+        <v>394</v>
+      </c>
+      <c r="D135" t="n" s="0">
+        <v>5250.0</v>
+      </c>
+      <c r="E135" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="F135" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="G135" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H135" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I135" t="n" s="0">
+        <v>504.510009765625</v>
+      </c>
+      <c r="J135" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>395</v>
+      </c>
+      <c r="B136" t="s" s="0">
+        <v>396</v>
+      </c>
+      <c r="C136" t="s" s="0">
+        <v>397</v>
+      </c>
+      <c r="D136" t="n" s="0">
+        <v>4314.0</v>
+      </c>
+      <c r="E136" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F136" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G136" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H136" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I136" t="n" s="0">
+        <v>381.567138671875</v>
+      </c>
+      <c r="J136" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>398</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>399</v>
+      </c>
+      <c r="C137" t="s" s="0">
+        <v>400</v>
+      </c>
+      <c r="D137" t="n" s="0">
+        <v>4479.0</v>
+      </c>
+      <c r="E137" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="F137" t="n" s="0">
         <v>10.0</v>
       </c>
-      <c r="G11" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H11" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n" s="0">
-        <v>68.90997314453125</v>
-      </c>
-      <c r="J11" t="b" s="0">
-        <v>1</v>
+      <c r="G137" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H137" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I137" t="n" s="0">
+        <v>355.4549865722656</v>
+      </c>
+      <c r="J137" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>401</v>
+      </c>
+      <c r="B138" t="s" s="0">
+        <v>402</v>
+      </c>
+      <c r="C138" t="s" s="0">
+        <v>403</v>
+      </c>
+      <c r="D138" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E138" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F138" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G138" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H138" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I138" t="n" s="0">
+        <v>1.7570000886917114</v>
+      </c>
+      <c r="J138" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="C139" t="s" s="0">
+        <v>406</v>
+      </c>
+      <c r="D139" t="n" s="0">
+        <v>862.0</v>
+      </c>
+      <c r="E139" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F139" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G139" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H139" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n" s="0">
+        <v>83.1709976196289</v>
+      </c>
+      <c r="J139" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
